--- a/excel-files/CALOOCAN/AMPARO HIGH SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/AMPARO HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\WEB\LR\excel-files\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="346" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{950007C0-4D27-4F8E-831E-B6ED926210D1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04428620-7C80-45CD-8766-7621B5E699F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -1835,13 +1835,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1865,6 +1858,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2943,13 +2943,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2986,6 +2979,13 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3028,7 +3028,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3045,7 +3045,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3101,7 +3101,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3474,17 +3474,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" customWidth="1"/>
+    <col min="3" max="5" width="24.8984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.09765625" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.95" customHeight="1">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="19.5">
+    <row r="6" spans="1:8" ht="19.2">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15">
+    <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="8"/>
@@ -3695,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.5">
+    <row r="12" spans="1:8" ht="19.2">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15">
+    <row r="13" spans="1:8">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="8"/>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.5">
+    <row r="19" spans="1:8" ht="19.2">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15">
+    <row r="20" spans="1:8">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="19.5">
+    <row r="23" spans="1:8" ht="19.2">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -5554,35 +5554,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
   <dimension ref="A1:AA127"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" customWidth="1"/>
+    <col min="3" max="3" width="17.09765625" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.09765625" customWidth="1"/>
+    <col min="6" max="6" width="24.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.59765625" customWidth="1"/>
+    <col min="8" max="9" width="20.8984375" customWidth="1"/>
+    <col min="10" max="10" width="13.69921875" customWidth="1"/>
+    <col min="11" max="11" width="35.59765625" customWidth="1"/>
+    <col min="12" max="12" width="24.8984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.59765625" customWidth="1"/>
+    <col min="14" max="15" width="20.8984375" customWidth="1"/>
+    <col min="16" max="16" width="21.59765625" customWidth="1"/>
+    <col min="17" max="17" width="33.3984375" customWidth="1"/>
+    <col min="18" max="18" width="25.8984375" customWidth="1"/>
+    <col min="19" max="19" width="32.8984375" customWidth="1"/>
+    <col min="20" max="21" width="20.8984375" customWidth="1"/>
+    <col min="22" max="22" width="16.09765625" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="24" max="24" width="15.296875" customWidth="1"/>
+    <col min="25" max="25" width="20.8984375" customWidth="1"/>
+    <col min="26" max="26" width="14.8984375" customWidth="1"/>
+    <col min="27" max="27" width="15.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.200000000000003" customHeight="1">
       <c r="D1" s="44" t="s">
         <v>33</v>
       </c>
@@ -5766,7 +5766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5778,7 +5778,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="38.25">
+    <row r="5" spans="1:27" ht="19.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="19.2">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="19.2">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="19.2">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="19.2">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="19.2">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.5">
+    <row r="11" spans="1:27" ht="19.2">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6261,7 +6261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.5">
+    <row r="12" spans="1:27" ht="19.2">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6343,7 +6343,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="38.25">
+    <row r="14" spans="1:27" ht="19.2">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6412,7 +6412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="19.2">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6481,7 +6481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="19.2">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="19.2">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="19.2">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="19.2">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.5">
+    <row r="20" spans="1:27" ht="19.2">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.5">
+    <row r="21" spans="1:27" ht="19.2">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6909,7 +6909,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="38.25">
+    <row r="23" spans="1:27" ht="19.2">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="19.2">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="19.2">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="19.2">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7185,7 +7185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="19.2">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="19.2">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7323,7 +7323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="19.2">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" ht="19.2">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7461,7 +7461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="31" spans="1:27" ht="19.2">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7544,7 +7544,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="19.2">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="19.2">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.5">
+    <row r="35" spans="1:27" ht="19.2">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="19.2">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="38.25">
+    <row r="37" spans="1:27" ht="19.2">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="19.2">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="19.2">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="19.2">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8096,7 +8096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="19.2">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8179,7 +8179,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="43" spans="1:27" ht="19.2">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="19.2">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8317,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="19.2">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="19.2">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="19.2">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="19.2">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="19.2">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="19.2">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="19.2">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8814,7 +8814,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="19.2">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" ht="19.2">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="55" spans="1:27" ht="19.2">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="19.2">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="38.25">
+    <row r="57" spans="1:27" ht="19.2">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="19.2">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.5">
+    <row r="59" spans="1:27" ht="19.2">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9297,7 +9297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="19.2">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9366,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="19.2">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9449,7 +9449,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.2">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="19.2">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="19.2">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9656,7 +9656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.5">
+    <row r="66" spans="1:27" ht="19.2">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="38.25">
+    <row r="67" spans="1:27" ht="19.2">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9794,7 +9794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.5">
+    <row r="68" spans="1:27" ht="19.2">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.5">
+    <row r="69" spans="1:27" ht="19.2">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -9932,7 +9932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.5">
+    <row r="70" spans="1:27" ht="19.2">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.5">
+    <row r="71" spans="1:27" ht="19.2">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10070,7 +10070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10084,7 +10084,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.5">
+    <row r="73" spans="1:27" ht="19.2">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10153,7 +10153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.5">
+    <row r="74" spans="1:27" ht="19.2">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.5">
+    <row r="75" spans="1:27" ht="19.2">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10291,7 +10291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.5">
+    <row r="76" spans="1:27" ht="19.2">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10360,7 +10360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.5">
+    <row r="77" spans="1:27" ht="19.2">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10429,7 +10429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.5">
+    <row r="78" spans="1:27" ht="19.2">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.5">
+    <row r="79" spans="1:27" ht="19.2">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.5">
+    <row r="80" spans="1:27" ht="19.2">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10636,7 +10636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.5">
+    <row r="81" spans="1:27" ht="19.2">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10719,7 +10719,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.5">
+    <row r="83" spans="1:27" ht="19.2">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10788,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.5">
+    <row r="84" spans="1:27" ht="19.2">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -10857,7 +10857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.5">
+    <row r="85" spans="1:27" ht="19.2">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -10926,7 +10926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.5">
+    <row r="86" spans="1:27" ht="19.2">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -10995,7 +10995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.5">
+    <row r="87" spans="1:27" ht="19.2">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.5">
+    <row r="88" spans="1:27" ht="19.2">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.5">
+    <row r="89" spans="1:27" ht="19.2">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.5">
+    <row r="90" spans="1:27" ht="19.2">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.5">
+    <row r="91" spans="1:27" ht="19.2">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11340,7 +11340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11354,7 +11354,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.5">
+    <row r="93" spans="1:27" ht="19.2">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11370,11 +11370,11 @@
       <c r="F93" s="10"/>
       <c r="G93" s="12"/>
       <c r="H93" s="12">
-        <f>IF((D93-E93)&lt;0,0,(D93-E93))</f>
+        <f t="shared" ref="H93:H101" si="24">IF((D93-E93)&lt;0,0,(D93-E93))</f>
         <v>0</v>
       </c>
       <c r="I93" s="12">
-        <f>IF((E93-D93)&lt;0,0,(E93-D93))</f>
+        <f t="shared" ref="I93:I101" si="25">IF((E93-D93)&lt;0,0,(E93-D93))</f>
         <v>0</v>
       </c>
       <c r="J93" s="12">
@@ -11385,11 +11385,11 @@
       <c r="L93" s="10"/>
       <c r="M93" s="12"/>
       <c r="N93" s="12">
-        <f>IF((J93-K93)&lt;0,0,(J93-K93))</f>
+        <f t="shared" ref="N93:N101" si="26">IF((J93-K93)&lt;0,0,(J93-K93))</f>
         <v>0</v>
       </c>
       <c r="O93" s="12">
-        <f>IF((K93-J93)&lt;0,0,(K93-J93))</f>
+        <f t="shared" ref="O93:O101" si="27">IF((K93-J93)&lt;0,0,(K93-J93))</f>
         <v>0</v>
       </c>
       <c r="P93" s="12">
@@ -11400,11 +11400,11 @@
       <c r="R93" s="10"/>
       <c r="S93" s="12"/>
       <c r="T93" s="12">
-        <f>IF((P93-Q93)&lt;0,0,(P93-Q93))</f>
+        <f t="shared" ref="T93:T101" si="28">IF((P93-Q93)&lt;0,0,(P93-Q93))</f>
         <v>0</v>
       </c>
       <c r="U93" s="12">
-        <f>IF((Q93-P93)&lt;0,0,(Q93-P93))</f>
+        <f t="shared" ref="U93:U101" si="29">IF((Q93-P93)&lt;0,0,(Q93-P93))</f>
         <v>0</v>
       </c>
       <c r="V93" s="12">
@@ -11415,15 +11415,15 @@
       <c r="X93" s="10"/>
       <c r="Y93" s="12"/>
       <c r="Z93" s="12">
-        <f>IF((V93-W93)&lt;0,0,(V93-W93))</f>
+        <f t="shared" ref="Z93:Z101" si="30">IF((V93-W93)&lt;0,0,(V93-W93))</f>
         <v>0</v>
       </c>
       <c r="AA93" s="12">
-        <f>IF((W93-V93)&lt;0,0,(W93-V93))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:27" ht="19.5">
+        <f t="shared" ref="AA93:AA101" si="31">IF((W93-V93)&lt;0,0,(W93-V93))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" ht="19.2">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11439,11 +11439,11 @@
       <c r="F94" s="10"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12">
-        <f>IF((D94-E94)&lt;0,0,(D94-E94))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I94" s="12">
-        <f>IF((E94-D94)&lt;0,0,(E94-D94))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J94" s="12">
@@ -11454,11 +11454,11 @@
       <c r="L94" s="10"/>
       <c r="M94" s="12"/>
       <c r="N94" s="12">
-        <f>IF((J94-K94)&lt;0,0,(J94-K94))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O94" s="12">
-        <f>IF((K94-J94)&lt;0,0,(K94-J94))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P94" s="12">
@@ -11469,11 +11469,11 @@
       <c r="R94" s="10"/>
       <c r="S94" s="12"/>
       <c r="T94" s="12">
-        <f>IF((P94-Q94)&lt;0,0,(P94-Q94))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U94" s="12">
-        <f>IF((Q94-P94)&lt;0,0,(Q94-P94))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V94" s="12">
@@ -11484,15 +11484,15 @@
       <c r="X94" s="10"/>
       <c r="Y94" s="12"/>
       <c r="Z94" s="12">
-        <f>IF((V94-W94)&lt;0,0,(V94-W94))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA94" s="12">
-        <f>IF((W94-V94)&lt;0,0,(W94-V94))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:27" ht="19.5">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" ht="19.2">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11508,11 +11508,11 @@
       <c r="F95" s="10"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12">
-        <f>IF((D95-E95)&lt;0,0,(D95-E95))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I95" s="12">
-        <f>IF((E95-D95)&lt;0,0,(E95-D95))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J95" s="12">
@@ -11523,11 +11523,11 @@
       <c r="L95" s="10"/>
       <c r="M95" s="12"/>
       <c r="N95" s="12">
-        <f>IF((J95-K95)&lt;0,0,(J95-K95))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O95" s="12">
-        <f>IF((K95-J95)&lt;0,0,(K95-J95))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P95" s="12">
@@ -11538,11 +11538,11 @@
       <c r="R95" s="10"/>
       <c r="S95" s="12"/>
       <c r="T95" s="12">
-        <f>IF((P95-Q95)&lt;0,0,(P95-Q95))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U95" s="12">
-        <f>IF((Q95-P95)&lt;0,0,(Q95-P95))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V95" s="12">
@@ -11553,15 +11553,15 @@
       <c r="X95" s="10"/>
       <c r="Y95" s="12"/>
       <c r="Z95" s="12">
-        <f>IF((V95-W95)&lt;0,0,(V95-W95))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA95" s="12">
-        <f>IF((W95-V95)&lt;0,0,(W95-V95))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:27" ht="19.5">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" ht="19.2">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11577,11 +11577,11 @@
       <c r="F96" s="10"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12">
-        <f>IF((D96-E96)&lt;0,0,(D96-E96))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I96" s="12">
-        <f>IF((E96-D96)&lt;0,0,(E96-D96))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J96" s="12">
@@ -11592,11 +11592,11 @@
       <c r="L96" s="10"/>
       <c r="M96" s="12"/>
       <c r="N96" s="12">
-        <f>IF((J96-K96)&lt;0,0,(J96-K96))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O96" s="12">
-        <f>IF((K96-J96)&lt;0,0,(K96-J96))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P96" s="12">
@@ -11607,11 +11607,11 @@
       <c r="R96" s="10"/>
       <c r="S96" s="12"/>
       <c r="T96" s="12">
-        <f>IF((P96-Q96)&lt;0,0,(P96-Q96))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U96" s="12">
-        <f>IF((Q96-P96)&lt;0,0,(Q96-P96))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V96" s="12">
@@ -11622,15 +11622,15 @@
       <c r="X96" s="10"/>
       <c r="Y96" s="12"/>
       <c r="Z96" s="12">
-        <f>IF((V96-W96)&lt;0,0,(V96-W96))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA96" s="12">
-        <f>IF((W96-V96)&lt;0,0,(W96-V96))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:27" ht="19.5">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" ht="19.2">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11646,11 +11646,11 @@
       <c r="F97" s="10"/>
       <c r="G97" s="12"/>
       <c r="H97" s="12">
-        <f>IF((D97-E97)&lt;0,0,(D97-E97))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I97" s="12">
-        <f>IF((E97-D97)&lt;0,0,(E97-D97))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J97" s="12">
@@ -11661,11 +11661,11 @@
       <c r="L97" s="10"/>
       <c r="M97" s="12"/>
       <c r="N97" s="12">
-        <f>IF((J97-K97)&lt;0,0,(J97-K97))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O97" s="12">
-        <f>IF((K97-J97)&lt;0,0,(K97-J97))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P97" s="12">
@@ -11676,11 +11676,11 @@
       <c r="R97" s="10"/>
       <c r="S97" s="12"/>
       <c r="T97" s="12">
-        <f>IF((P97-Q97)&lt;0,0,(P97-Q97))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U97" s="12">
-        <f>IF((Q97-P97)&lt;0,0,(Q97-P97))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V97" s="12">
@@ -11691,15 +11691,15 @@
       <c r="X97" s="10"/>
       <c r="Y97" s="12"/>
       <c r="Z97" s="12">
-        <f>IF((V97-W97)&lt;0,0,(V97-W97))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA97" s="12">
-        <f>IF((W97-V97)&lt;0,0,(W97-V97))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:27" ht="19.5">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" ht="19.2">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11715,11 +11715,11 @@
       <c r="F98" s="10"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12">
-        <f>IF((D98-E98)&lt;0,0,(D98-E98))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I98" s="12">
-        <f>IF((E98-D98)&lt;0,0,(E98-D98))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J98" s="12">
@@ -11730,11 +11730,11 @@
       <c r="L98" s="10"/>
       <c r="M98" s="12"/>
       <c r="N98" s="12">
-        <f>IF((J98-K98)&lt;0,0,(J98-K98))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O98" s="12">
-        <f>IF((K98-J98)&lt;0,0,(K98-J98))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P98" s="12">
@@ -11745,11 +11745,11 @@
       <c r="R98" s="10"/>
       <c r="S98" s="12"/>
       <c r="T98" s="12">
-        <f>IF((P98-Q98)&lt;0,0,(P98-Q98))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U98" s="12">
-        <f>IF((Q98-P98)&lt;0,0,(Q98-P98))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V98" s="12">
@@ -11760,15 +11760,15 @@
       <c r="X98" s="10"/>
       <c r="Y98" s="12"/>
       <c r="Z98" s="12">
-        <f>IF((V98-W98)&lt;0,0,(V98-W98))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA98" s="12">
-        <f>IF((W98-V98)&lt;0,0,(W98-V98))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:27" ht="19.5">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" ht="19.2">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11784,11 +11784,11 @@
       <c r="F99" s="10"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12">
-        <f>IF((D99-E99)&lt;0,0,(D99-E99))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I99" s="12">
-        <f>IF((E99-D99)&lt;0,0,(E99-D99))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J99" s="12">
@@ -11799,11 +11799,11 @@
       <c r="L99" s="10"/>
       <c r="M99" s="12"/>
       <c r="N99" s="12">
-        <f>IF((J99-K99)&lt;0,0,(J99-K99))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O99" s="12">
-        <f>IF((K99-J99)&lt;0,0,(K99-J99))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P99" s="12">
@@ -11814,11 +11814,11 @@
       <c r="R99" s="10"/>
       <c r="S99" s="12"/>
       <c r="T99" s="12">
-        <f>IF((P99-Q99)&lt;0,0,(P99-Q99))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U99" s="12">
-        <f>IF((Q99-P99)&lt;0,0,(Q99-P99))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V99" s="12">
@@ -11829,15 +11829,15 @@
       <c r="X99" s="10"/>
       <c r="Y99" s="12"/>
       <c r="Z99" s="12">
-        <f>IF((V99-W99)&lt;0,0,(V99-W99))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA99" s="12">
-        <f>IF((W99-V99)&lt;0,0,(W99-V99))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:27" ht="19.5">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" ht="19.2">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -11853,11 +11853,11 @@
       <c r="F100" s="10"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12">
-        <f>IF((D100-E100)&lt;0,0,(D100-E100))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I100" s="12">
-        <f>IF((E100-D100)&lt;0,0,(E100-D100))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J100" s="12">
@@ -11868,11 +11868,11 @@
       <c r="L100" s="10"/>
       <c r="M100" s="12"/>
       <c r="N100" s="12">
-        <f>IF((J100-K100)&lt;0,0,(J100-K100))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O100" s="12">
-        <f>IF((K100-J100)&lt;0,0,(K100-J100))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P100" s="12">
@@ -11883,11 +11883,11 @@
       <c r="R100" s="10"/>
       <c r="S100" s="12"/>
       <c r="T100" s="12">
-        <f>IF((P100-Q100)&lt;0,0,(P100-Q100))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U100" s="12">
-        <f>IF((Q100-P100)&lt;0,0,(Q100-P100))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V100" s="12">
@@ -11898,15 +11898,15 @@
       <c r="X100" s="10"/>
       <c r="Y100" s="12"/>
       <c r="Z100" s="12">
-        <f>IF((V100-W100)&lt;0,0,(V100-W100))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA100" s="12">
-        <f>IF((W100-V100)&lt;0,0,(W100-V100))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:27" ht="19.5">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" ht="19.2">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -11922,11 +11922,11 @@
       <c r="F101" s="10"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12">
-        <f>IF((D101-E101)&lt;0,0,(D101-E101))</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I101" s="12">
-        <f>IF((E101-D101)&lt;0,0,(E101-D101))</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J101" s="12">
@@ -11937,11 +11937,11 @@
       <c r="L101" s="10"/>
       <c r="M101" s="12"/>
       <c r="N101" s="12">
-        <f>IF((J101-K101)&lt;0,0,(J101-K101))</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="O101" s="12">
-        <f>IF((K101-J101)&lt;0,0,(K101-J101))</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="P101" s="12">
@@ -11952,11 +11952,11 @@
       <c r="R101" s="10"/>
       <c r="S101" s="12"/>
       <c r="T101" s="12">
-        <f>IF((P101-Q101)&lt;0,0,(P101-Q101))</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="U101" s="12">
-        <f>IF((Q101-P101)&lt;0,0,(Q101-P101))</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="V101" s="12">
@@ -11967,15 +11967,15 @@
       <c r="X101" s="10"/>
       <c r="Y101" s="12"/>
       <c r="Z101" s="12">
-        <f>IF((V101-W101)&lt;0,0,(V101-W101))</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA101" s="12">
-        <f>IF((W101-V101)&lt;0,0,(W101-V101))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -11989,7 +11989,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.4">
       <c r="A103" s="1" t="s">
         <v>24</v>
       </c>
@@ -12058,7 +12058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.5">
+    <row r="104" spans="1:27" ht="19.2">
       <c r="A104" s="1" t="s">
         <v>24</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.5">
+    <row r="105" spans="1:27" ht="19.2">
       <c r="A105" s="1" t="s">
         <v>24</v>
       </c>
@@ -12196,7 +12196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.5">
+    <row r="106" spans="1:27" ht="19.2">
       <c r="A106" s="1" t="s">
         <v>24</v>
       </c>
@@ -12265,7 +12265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.25">
+    <row r="107" spans="1:27" ht="38.4">
       <c r="A107" s="1" t="s">
         <v>24</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="38.25">
+    <row r="108" spans="1:27" ht="19.2">
       <c r="A108" s="1" t="s">
         <v>24</v>
       </c>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="57.75">
+    <row r="109" spans="1:27" ht="38.4">
       <c r="A109" s="1" t="s">
         <v>24</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.25">
+    <row r="110" spans="1:27" ht="38.4">
       <c r="A110" s="1" t="s">
         <v>24</v>
       </c>
@@ -12541,7 +12541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.5">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.2">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12552,7 +12552,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.5">
+    <row r="112" spans="1:27" ht="19.2">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12614,7 +12614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.5">
+    <row r="113" spans="1:27" ht="19.2">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12676,7 +12676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.5">
+    <row r="114" spans="1:27" ht="19.2">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12738,7 +12738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.5">
+    <row r="115" spans="1:27" ht="19.2">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12800,7 +12800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.5">
+    <row r="116" spans="1:27" ht="19.2">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -12862,7 +12862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.5">
+    <row r="117" spans="1:27" ht="19.2">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -12924,7 +12924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.5">
+    <row r="118" spans="1:27" ht="19.2">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -12986,7 +12986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.5">
+    <row r="119" spans="1:27" ht="19.2">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13048,7 +13048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.5">
+    <row r="120" spans="1:27" ht="19.2">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13110,7 +13110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.5">
+    <row r="121" spans="1:27" ht="19.2">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13172,7 +13172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.5">
+    <row r="122" spans="1:27" ht="19.2">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13234,7 +13234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.5">
+    <row r="123" spans="1:27" ht="19.2">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13296,7 +13296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.5">
+    <row r="124" spans="1:27" ht="19.2">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13358,7 +13358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.5">
+    <row r="125" spans="1:27" ht="19.2">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13420,7 +13420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.5">
+    <row r="126" spans="1:27" ht="19.2">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13482,7 +13482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.5">
+    <row r="127" spans="1:27" ht="19.2">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13506,11 +13506,11 @@
       <c r="L127" s="29"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
-        <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
+        <f t="shared" ref="N127" si="32">IF((J127-K127)&lt;0,0,(J127-K127))</f>
         <v>0</v>
       </c>
       <c r="O127" s="5">
-        <f t="shared" ref="O127" si="25">IF((K127-J127)&lt;0,0,(K127-J127))</f>
+        <f t="shared" ref="O127" si="33">IF((K127-J127)&lt;0,0,(K127-J127))</f>
         <v>0</v>
       </c>
       <c r="P127" s="5"/>
@@ -13554,21 +13554,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 X112:X127 X83:X91 X93:X101 X14:X21 X5:X12 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F53:F61 F43:F51 F33:F41 F23:F31 F5:F12 F14:F21 F93:F101 F83:F91 F63:F71 F73:F81 F103:F110 F112:F127" xr:uid="{81A39530-E325-4B0C-8D02-8D3897A14837}">
       <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127" xr:uid="{BCA642C0-6AD3-439B-AA3C-715708A97158}">
-      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13584,34 +13581,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
   <dimension ref="A1:AB140"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" style="41" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" style="41" customWidth="1"/>
+    <col min="3" max="3" width="17.09765625" customWidth="1"/>
+    <col min="4" max="4" width="16.3984375" customWidth="1"/>
+    <col min="5" max="5" width="23.09765625" customWidth="1"/>
+    <col min="6" max="6" width="24.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.59765625" customWidth="1"/>
+    <col min="8" max="9" width="20.8984375" customWidth="1"/>
+    <col min="10" max="10" width="13.69921875" customWidth="1"/>
+    <col min="11" max="11" width="24.3984375" customWidth="1"/>
+    <col min="12" max="12" width="18.09765625" customWidth="1"/>
+    <col min="13" max="15" width="20.8984375" customWidth="1"/>
+    <col min="16" max="16" width="21.59765625" customWidth="1"/>
+    <col min="17" max="17" width="29.09765625" customWidth="1"/>
+    <col min="18" max="18" width="25.8984375" customWidth="1"/>
+    <col min="19" max="19" width="32.8984375" customWidth="1"/>
+    <col min="20" max="21" width="20.8984375" customWidth="1"/>
+    <col min="22" max="22" width="16.09765625" customWidth="1"/>
     <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="24" max="24" width="15.296875" customWidth="1"/>
+    <col min="25" max="25" width="20.8984375" customWidth="1"/>
+    <col min="26" max="26" width="14.8984375" customWidth="1"/>
+    <col min="27" max="27" width="15.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.200000000000003" customHeight="1">
       <c r="B1" s="39"/>
       <c r="D1" s="44" t="s">
         <v>33</v>
@@ -13729,7 +13726,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="38.25">
+    <row r="3" spans="1:27" ht="38.4">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13760,11 +13757,11 @@
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
-        <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
+        <f t="shared" ref="N3:N70" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
         <v>0</v>
       </c>
       <c r="O3" s="5">
-        <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
+        <f t="shared" ref="O3:O70" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
         <v>0</v>
       </c>
       <c r="P3" s="5">
@@ -13798,7 +13795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.5">
+    <row r="4" spans="1:27" ht="19.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13867,7 +13864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.5">
+    <row r="5" spans="1:27" ht="19.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13936,7 +13933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="19.2">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14005,7 +14002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="19.2">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14074,7 +14071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="19.2">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14143,7 +14140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="19.2">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14212,7 +14209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="19.2">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14284,7 +14281,7 @@
     <row r="11" spans="1:27" s="7" customFormat="1">
       <c r="B11" s="40"/>
     </row>
-    <row r="12" spans="1:27" ht="38.25">
+    <row r="12" spans="1:27" ht="38.4">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14353,7 +14350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.5">
+    <row r="13" spans="1:27" ht="19.2">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14422,7 +14419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.5">
+    <row r="14" spans="1:27" ht="19.2">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14491,7 +14488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="19.2">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14560,7 +14557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="19.2">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14629,7 +14626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="19.2">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14698,7 +14695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="19.2">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14767,7 +14764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="19.2">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14839,7 +14836,7 @@
     <row r="20" spans="1:27" s="7" customFormat="1">
       <c r="B20" s="40"/>
     </row>
-    <row r="21" spans="1:27" ht="38.25">
+    <row r="21" spans="1:27" ht="19.2">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14908,7 +14905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.5">
+    <row r="22" spans="1:27" ht="19.2">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -14977,7 +14974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.5">
+    <row r="23" spans="1:27" ht="19.2">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15046,7 +15043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="19.2">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15115,7 +15112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="19.2">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15184,7 +15181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="19.2">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15253,7 +15250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="19.2">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15322,7 +15319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="19.2">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15391,7 +15388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="19.2">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15463,7 +15460,7 @@
     <row r="30" spans="1:27" s="7" customFormat="1">
       <c r="B30" s="40"/>
     </row>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="31" spans="1:27" ht="19.2">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15532,7 +15529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.5">
+    <row r="32" spans="1:27" ht="19.2">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15601,7 +15598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="19.2">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15670,7 +15667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="19.2">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15739,7 +15736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="38.25">
+    <row r="35" spans="1:27" ht="19.2">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15808,7 +15805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="19.2">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15877,7 +15874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.5">
+    <row r="37" spans="1:27" ht="19.2">
       <c r="A37" s="36">
         <v>4</v>
       </c>
@@ -15946,7 +15943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="19.2">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16015,7 +16012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="19.2">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16084,7 +16081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="19.2">
       <c r="A40" s="36">
         <v>4</v>
       </c>
@@ -16153,7 +16150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="19.2">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16225,7 +16222,7 @@
     <row r="42" spans="1:27" s="7" customFormat="1">
       <c r="B42" s="40"/>
     </row>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="43" spans="1:27" ht="19.2">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16294,7 +16291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="19.2">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16363,7 +16360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="19.2">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16432,7 +16429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="19.2">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16501,7 +16498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="19.2">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16570,7 +16567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="19.2">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16639,7 +16636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="19.2">
       <c r="A49" s="36">
         <v>5</v>
       </c>
@@ -16708,7 +16705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="19.2">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16777,7 +16774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="19.2">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16846,7 +16843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.5">
+    <row r="52" spans="1:27" ht="19.2">
       <c r="A52" s="36">
         <v>5</v>
       </c>
@@ -16915,7 +16912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="19.2">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -16987,7 +16984,7 @@
     <row r="54" spans="1:27" s="7" customFormat="1">
       <c r="B54" s="40"/>
     </row>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="55" spans="1:27" ht="19.2">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17056,7 +17053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="19.2">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17125,7 +17122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.5">
+    <row r="57" spans="1:27" ht="19.2">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17194,7 +17191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="19.2">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17263,7 +17260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25">
+    <row r="59" spans="1:27" ht="19.2">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17332,7 +17329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="19.2">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17401,7 +17398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="19.2">
       <c r="A61" s="36">
         <v>6</v>
       </c>
@@ -17470,7 +17467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.5">
+    <row r="62" spans="1:27" ht="19.2">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17539,7 +17536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.5">
+    <row r="63" spans="1:27" ht="19.2">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17608,7 +17605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="19.2">
       <c r="A64" s="36">
         <v>6</v>
       </c>
@@ -17677,7 +17674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="19.2">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -17749,7 +17746,7 @@
     <row r="66" spans="1:27" s="7" customFormat="1">
       <c r="B66" s="40"/>
     </row>
-    <row r="67" spans="1:27" ht="19.5">
+    <row r="67" spans="1:27" ht="19.2">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -17820,7 +17817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.5">
+    <row r="68" spans="1:27" ht="19.2">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -17891,7 +17888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.5">
+    <row r="69" spans="1:27" ht="19.2">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -17962,7 +17959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.5">
+    <row r="70" spans="1:27" ht="19.2">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18033,7 +18030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="38.25">
+    <row r="71" spans="1:27" ht="19.2">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18104,7 +18101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.5">
+    <row r="72" spans="1:27" ht="19.2">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18175,7 +18172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.5">
+    <row r="73" spans="1:27" ht="19.2">
       <c r="A73" s="37">
         <v>7</v>
       </c>
@@ -18246,7 +18243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.5">
+    <row r="74" spans="1:27" ht="19.2">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18317,7 +18314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.5">
+    <row r="75" spans="1:27" ht="19.2">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18388,7 +18385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.5">
+    <row r="76" spans="1:27" ht="19.2">
       <c r="A76" s="37">
         <v>7</v>
       </c>
@@ -18459,7 +18456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.5">
+    <row r="77" spans="1:27" ht="19.2">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18533,7 +18530,7 @@
     <row r="78" spans="1:27" s="7" customFormat="1">
       <c r="B78" s="40"/>
     </row>
-    <row r="79" spans="1:27" ht="19.5">
+    <row r="79" spans="1:27" ht="19.2">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -18570,11 +18567,11 @@
       <c r="L79" s="10"/>
       <c r="M79" s="12"/>
       <c r="N79" s="12">
-        <f t="shared" ref="N74:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
+        <f t="shared" ref="N79:N122" si="20">IF((J79-K79)&lt;0,0,(J79-K79))</f>
         <v>6440</v>
       </c>
       <c r="O79" s="12">
-        <f t="shared" ref="O74:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
+        <f t="shared" ref="O79:O122" si="21">IF((K79-J79)&lt;0,0,(K79-J79))</f>
         <v>0</v>
       </c>
       <c r="P79" s="12">
@@ -18608,7 +18605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.5">
+    <row r="80" spans="1:27" ht="19.2">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18683,7 +18680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.5">
+    <row r="81" spans="1:27" ht="19.2">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18758,7 +18755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.5">
+    <row r="82" spans="1:27" ht="19.2">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18833,7 +18830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.5">
+    <row r="83" spans="1:27" ht="19.2">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18904,7 +18901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.5">
+    <row r="84" spans="1:27" ht="19.2">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -18979,7 +18976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.5">
+    <row r="85" spans="1:27" ht="19.2">
       <c r="A85" s="37">
         <v>8</v>
       </c>
@@ -19054,7 +19051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.5">
+    <row r="86" spans="1:27" ht="19.2">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19129,7 +19126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.5">
+    <row r="87" spans="1:27" ht="19.2">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19204,7 +19201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.5">
+    <row r="88" spans="1:27" ht="19.2">
       <c r="A88" s="37">
         <v>8</v>
       </c>
@@ -19279,7 +19276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.5">
+    <row r="89" spans="1:27" ht="19.2">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19357,7 +19354,7 @@
     <row r="90" spans="1:27" s="7" customFormat="1">
       <c r="B90" s="40"/>
     </row>
-    <row r="91" spans="1:27" ht="19.5">
+    <row r="91" spans="1:27" ht="19.2">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19428,7 +19425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.5">
+    <row r="92" spans="1:27" ht="19.2">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19511,7 +19508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.5">
+    <row r="93" spans="1:27" ht="19.2">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19594,7 +19591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.5">
+    <row r="94" spans="1:27" ht="19.2">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19669,7 +19666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.5">
+    <row r="95" spans="1:27" ht="19.2">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -19744,7 +19741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.5">
+    <row r="96" spans="1:27" ht="19.2">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -19819,7 +19816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.5">
+    <row r="97" spans="1:27" ht="19.2">
       <c r="A97" s="37">
         <v>9</v>
       </c>
@@ -19890,7 +19887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.5">
+    <row r="98" spans="1:27" ht="19.2">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -19961,7 +19958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.5">
+    <row r="99" spans="1:27" ht="19.2">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20032,7 +20029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.5">
+    <row r="100" spans="1:27" ht="19.2">
       <c r="A100" s="37">
         <v>9</v>
       </c>
@@ -20107,7 +20104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.5">
+    <row r="101" spans="1:27" ht="19.2">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20185,7 +20182,7 @@
     <row r="102" spans="1:27" s="7" customFormat="1">
       <c r="B102" s="40"/>
     </row>
-    <row r="103" spans="1:27" ht="19.5">
+    <row r="103" spans="1:27" ht="19.2">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20272,7 +20269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.5">
+    <row r="104" spans="1:27" ht="19.2">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20355,7 +20352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.5">
+    <row r="105" spans="1:27" ht="19.2">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20442,7 +20439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.5">
+    <row r="106" spans="1:27" ht="19.2">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20521,7 +20518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.5">
+    <row r="107" spans="1:27" ht="19.2">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20600,7 +20597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.5">
+    <row r="108" spans="1:27" ht="19.2">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20679,7 +20676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.5">
+    <row r="109" spans="1:27" ht="19.2">
       <c r="A109" s="37">
         <v>10</v>
       </c>
@@ -20758,7 +20755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.5">
+    <row r="110" spans="1:27" ht="19.2">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -20837,7 +20834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.5">
+    <row r="111" spans="1:27" ht="19.2">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -20912,7 +20909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.5">
+    <row r="112" spans="1:27" ht="19.2">
       <c r="A112" s="37">
         <v>10</v>
       </c>
@@ -20991,7 +20988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.5">
+    <row r="113" spans="1:28" ht="19.2">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -21073,7 +21070,7 @@
     <row r="114" spans="1:28" s="7" customFormat="1">
       <c r="B114" s="40"/>
     </row>
-    <row r="115" spans="1:28" ht="38.25">
+    <row r="115" spans="1:28" ht="38.4">
       <c r="A115" s="1" t="s">
         <v>24</v>
       </c>
@@ -21144,7 +21141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.5">
+    <row r="116" spans="1:28" ht="19.2">
       <c r="A116" s="1" t="s">
         <v>24</v>
       </c>
@@ -21215,7 +21212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.5">
+    <row r="117" spans="1:28" ht="19.2">
       <c r="A117" s="1" t="s">
         <v>24</v>
       </c>
@@ -21286,7 +21283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.5">
+    <row r="118" spans="1:28" ht="19.2">
       <c r="A118" s="1" t="s">
         <v>24</v>
       </c>
@@ -21357,7 +21354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.25">
+    <row r="119" spans="1:28" ht="38.4">
       <c r="A119" s="1" t="s">
         <v>24</v>
       </c>
@@ -21428,7 +21425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="38.25">
+    <row r="120" spans="1:28" ht="19.2">
       <c r="A120" s="1" t="s">
         <v>24</v>
       </c>
@@ -21499,7 +21496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="57.75">
+    <row r="121" spans="1:28" ht="38.4">
       <c r="A121" s="1" t="s">
         <v>24</v>
       </c>
@@ -21570,7 +21567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.25">
+    <row r="122" spans="1:28" ht="38.4">
       <c r="A122" s="1" t="s">
         <v>24</v>
       </c>
@@ -22171,8 +22168,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 R91:R101 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R103:R113 L115:L122 R12:R19 R3:R10 X103:X113 X115:X122 R115:R122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F55:F65 F43:F53 F115:F122 F21:F29 F31:F41 F67:F77 F79:F89 F91:F101 F103:F113 F3:F10 F12:F19" xr:uid="{6B6075B3-CF64-47D2-87ED-2B34A5249DFA}">
       <formula1>"2024,2025,2026"</formula1>
